--- a/data/kz/niches/niche_formats_REPAIR_PHONE.xlsx
+++ b/data/kz/niches/niche_formats_REPAIR_PHONE.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -641,12 +642,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -692,12 +693,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -768,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,12 +825,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -861,12 +863,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -899,12 +901,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -937,12 +939,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1007,6 +1009,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1057,12 +1060,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1090,12 +1093,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1158,6 +1161,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1257,6 +1261,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1571,6 +1576,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1696,6 +1702,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1776,12 +1783,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1835,12 +1842,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1894,12 +1901,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1999,6 +2006,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2119,12 +2127,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2194,12 +2202,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2269,12 +2277,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2380,6 +2388,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2450,12 +2459,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2497,12 +2506,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2540,12 +2549,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2619,6 +2628,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2689,12 +2699,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2734,12 +2744,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2779,12 +2789,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2857,6 +2867,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2912,12 +2923,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2954,12 +2965,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2996,12 +3007,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3074,6 +3085,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3144,12 +3156,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3205,12 +3217,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3266,12 +3278,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3358,6 +3370,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3403,12 +3416,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3437,12 +3450,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3471,12 +3484,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3505,12 +3518,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>REP_KIOSK</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3566,6 +3579,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3591,12 +3605,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3613,12 +3627,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REP_SHOP</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
